--- a/My portfolio.xlsx
+++ b/My portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Portfolio\Handover-20260625T210137Z-3-001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F75C81D-4B84-4AD7-85C5-023E7916547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{046A62C4-7C07-46EB-A98B-F1896C4878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79ED3A2B-08A0-4AB3-AA7B-289E1BF298E0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="108">
   <si>
     <t>Project Name</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t xml:space="preserve">Adobe Premiere Pro -Color correction - AI generation </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/r/1QZJkQPaGy/</t>
   </si>
   <si>
     <t>Teleperformance Egypt – Ramadan Charity Campaign</t>
@@ -1546,98 +1549,100 @@
       <c r="F30" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="14"/>
+      <c r="G30" s="13" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="31" spans="1:7" ht="152.25">
       <c r="A31" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="121.5">
       <c r="A32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="167.25">
       <c r="A33" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="183">
       <c r="A34" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1718,8 +1723,9 @@
     <hyperlink ref="G32" r:id="rId44" xr:uid="{A6E44525-37D8-4766-83B4-B6027DEC77FA}"/>
     <hyperlink ref="G33" r:id="rId45" xr:uid="{0D17FB24-10E5-48B8-BD09-38E9A642FBEA}"/>
     <hyperlink ref="B34" r:id="rId46" xr:uid="{E838C6F8-2138-4387-ACDC-A27BBFB44E3B}"/>
+    <hyperlink ref="G30" r:id="rId47" xr:uid="{A4D831B2-0A55-49EB-834C-4393193A13D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId47"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId48"/>
 </worksheet>
 </file>
--- a/My portfolio.xlsx
+++ b/My portfolio.xlsx
@@ -1,41 +1,31 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Portfolio\Handover-20260625T210137Z-3-001\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{046A62C4-7C07-46EB-A98B-F1896C4878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79ED3A2B-08A0-4AB3-AA7B-289E1BF298E0}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel Online</Application>
+  <Manager/>
+  <Company/>
+  <HyperlinkBase/>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:title/>
+  <dc:subject/>
+  <dc:creator>Islam Mohamed</dc:creator>
+  <cp:keywords/>
+  <dc:description/>
+  <cp:lastModifiedBy/>
+  <cp:revision/>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-06-25T23:08:56Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-29T09:27:26Z</dcterms:modified>
+  <cp:category/>
+  <cp:contentStatus/>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="108">
   <si>
     <t>Project Name</t>
@@ -62,7 +52,7 @@
     <t>Strang Lila Short Film</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1pMGdnYhXO7o1WCA82hhSVpr7nt7o0VBZ/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/7c4debd8-c75a-4184-ade8-53ad10bc0cf1</t>
   </si>
   <si>
     <t>Video Editing - Translation</t>
@@ -81,7 +71,7 @@
     <t>lonly Mother Short Film</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1EkgmoOU-8p2RAKrf_5D71I7_7DKPLdUi/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/21a98d76-9ef0-4359-ac95-7a6cb7d9ebfe</t>
   </si>
   <si>
     <t>Video Editing - Color Grading</t>
@@ -98,7 +88,7 @@
     <t>Cancer Heros</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1M0zXIeSvIDBNcu0E0jpXpjUau6taC5LM/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/ca795e15-fa6c-4460-9566-d0cc605cb02c</t>
   </si>
   <si>
     <t>A touching music video dedicated to children battling cancer, portraying them as resilient heroes through creative play like boxing or acting as doctors. The video highlights their inspiring strength and fighting spirit.
@@ -109,7 +99,7 @@
     <t>Out Of Z Box</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1BHsLvLA2-g9sJZHehnSV9BNMDe4FfJ9O/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/af8fd05e-0728-4afe-b95b-4a11ee7ed629</t>
   </si>
   <si>
     <t>A high-energy corporate video created for an internal company event, designed entirely to inspire and motivate employees. Built 100% from curated stock footage, the project aimed to drive innovative thinking.
@@ -120,7 +110,7 @@
     <t xml:space="preserve">Strang Lila Short Film trailer </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1ls1Jd9tTaW7axUD8Ey7lmj0LAj9TiXME/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/233f4e7e-9851-4df5-9a19-994f477c825f</t>
   </si>
   <si>
     <t>A high-tension, fast-paced trailer designed to tease the emotional and dramatic arc of the short film "Layla." The goal was to build intense curiosity around her imprisonment and the social isolation she faces upon release.
@@ -135,7 +125,7 @@
     <t>The ballet girls</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1XlQdXfbkVtkUtOTXTOTxsw2zJKPK9DIq/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/b94151ec-a59e-445f-a5c2-1d9cd05972f0</t>
   </si>
   <si>
     <t>A captivating visual piece that pulls back the curtain on the world of ballet, capturing the dedication, intense exhaustion, and physical struggles dancers endure during training.
@@ -146,7 +136,7 @@
     <t>Newberry Short film</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1BNz4QaelfFRHiPLnjMrTTYe_BdthyL7y/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/a8213a9f-32bd-4bfb-92d8-facbb3dc4cd1</t>
   </si>
   <si>
     <t>Translation</t>
@@ -163,7 +153,7 @@
     <t xml:space="preserve">Masrya Short film </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1VG9VgbMJtQMLtA-J7p7EmKEeNAhhyBJe/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/72c22c06-4d6c-4c3f-940a-88c7e75f71f8</t>
   </si>
   <si>
     <t>A compelling anthology short film that highlights the vital role of women in Egyptian society by weaving together the distinct stories of multiple unique characters.
@@ -175,7 +165,7 @@
     <t xml:space="preserve">BS Perfumes </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1xPTelvjDZe03GKDMGiVNnsNIU9P0vv9e/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/50475a6c-98b6-4cf5-9962-3b1a2eb8d7c1</t>
   </si>
   <si>
     <t>A cinematic and high-end commercial video showcasing the luxurious fragrance collection of an Emirati brand, designed with a sophisticated and premium visual aesthetic.
@@ -190,7 +180,7 @@
     <t>BS hospitality</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1wOpWc7CQxgcc8DxcPZe4LYP9ZQU3yP2_/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/5b4073b6-ab28-4253-8d58-2667dffa0090</t>
   </si>
   <si>
     <t>A sophisticated promotional video showcasing an Emirati company specializing in premium wedding and event hospitality, designed to reflect their high-end service and luxury standards.
@@ -202,13 +192,13 @@
     <t>BS Perfumes 2</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1kOyWpq03X4MoqDH55xm196e04FdY1tKI/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/196b0ab0-a7f1-4ac8-9ec4-bad50496e590</t>
   </si>
   <si>
     <t>Mohammed Shami – Influencer Content (Translation)</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/12VpCjdZInGjsOM-1N8Mx34L2t18CEDMT/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/80c0398f-1035-4a20-a642-2779f98bb0fc</t>
   </si>
   <si>
     <t>A series of engaging food vlogs for the well-known Egyptian influencer Mohammed Shami, reviewing diverse restaurants across the United States with the goal of expanding his audience and breaking into the US market.
@@ -219,7 +209,7 @@
     <t>https://www.facebook.com/share/v/18gtEfcuSt/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1fG8645G8_VEXYxSky9QnEpeflB5YGQGG/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/7a00fe47-0f2e-40a3-aac1-d0a84a16dfb8</t>
   </si>
   <si>
     <t>A series of engaging food vlogs for the well-known Egyptian influencer Mohammed Shami, reviewing diverse restaurants across the United States with the goal of expanding his audience and breaking into the US market.
@@ -230,91 +220,91 @@
     <t>https://www.facebook.com/share/v/17d3jqvn3V/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1jyjayaP2sPxziyjwDCzEwLL--J81d9FN/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/43ae99b2-5b2e-43ed-9319-ab13e8ede555</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1D71ChjMrU/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1staSZySInlcOgHhDlz5AVC89VTiUSG25/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/19621351-7aea-497c-a091-4ae5a3cd495c</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1FAQ27dsoX/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1OX5uol2j55cDx-w7U-HRrcSLoqjpdK9s/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/1c7b994f-93f0-4fb6-8b5b-046a2787ac25</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/938147480875096</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1WC_FMj0wUaVnVa10XK_Usx0gDODKNyAj/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/061ac5b8-139d-45c7-9275-80622c5e064d</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/1763089927546647</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1QouY1mFICqBKagysze0CZ8laA3uzZTuU/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/5c1fcdec-fe01-4ec2-82e6-a4c17e407bab</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/17cchSfkc1/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1B5dMYrEyKA3dH9udQTyz1HOI8KuVxtOP/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/bad791a7-f157-4c8c-9243-fbb45ed4e648</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/397823062876992</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1vEb6v5v4i7kjLpSE6006MVnCASs8Slzh/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/3146f189-8a95-4f2b-b480-3fb197dea58b</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1JU66mVZfz/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Sp7OmtQ_yNITTFkxVMdhT3UAhmOYIbEO/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/fbe8887b-afb0-4a76-9419-d7f086f8a1c3</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1W6B1PPbt9/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1MOOIoS33HawAZPffasFyA7qi_nD80i4R/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/af10350f-558d-451a-8811-4a28f9edcd22</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/887708776538856</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1EtqeSct5W17WEXODEtj43jufK2HYCLNz/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/df3765b9-2148-412f-ada4-f3a4de0a27b5</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1ChG1sZPHc/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1M4ckzltGXLETnkeu9eah2oSev1sqk-yS/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/22799f6b-a0f1-4cd6-8b95-2debe25976e0</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/18MCDBAe9j/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1b8JUtTRCIfUWfUPyXHHD1_xyTJzwRI9v/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/a6b37e75-beb2-40fe-8b89-5085be7d2d5b</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/357597543504090</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1vtKXvuGHrv11oetqtiwg9Imw2X8_2nkb/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/2d746e7e-4715-4005-939f-98312b43ad3b</t>
   </si>
   <si>
     <t>https://www.facebook.com/share/v/193MWbSZWN/</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1BRE0YwKa8w5iUrEEDED0vIz5kOMb_Xap/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/316500bc-45b2-4f1f-aca6-82ddbf5c4dcc</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/940250344253167</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1aRX8UqumMAm1jXZSWE5o4Z00VaALjEac/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/21344783-ce27-45d4-8d35-eec56cf1f075</t>
   </si>
   <si>
     <t>https://www.facebook.com/reel/414288234542459</t>
@@ -323,7 +313,7 @@
     <t>Teleperformance Egypt – Eid Al-Fitr Campaign</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/15qTuTJ2N0TUmqV43ZHJaic8KtdVQARr5/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/492da76a-ebf1-4de0-a92a-81f2617892e5</t>
   </si>
   <si>
     <t>A unique, fully AI-generated festive video created for Teleperformance Egypt to celebrate Eid Al-Fitr, designed to capture the holiday's joyful spirit through cutting-edge technology.
@@ -343,7 +333,7 @@
     <t>Teleperformance Egypt – Ramadan Charity Campaign</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1cOmuUZCvNKlprkDOz2CPvEj0mTr90_9S/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/19ad534b-93f0-433b-9fa8-dac091fc9181</t>
   </si>
   <si>
     <t>A heartwarming corporate social responsibility (CSR) video documenting Teleperformance Egypt's charity event, where employees gathered to pack Ramadan food boxes for families in need.
@@ -360,7 +350,7 @@
     <t>Teleperformance Egypt – Sports Tournament</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Nif0Q8OV-bJix240KO1KPnWR0Tangc1Y/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/efc301ed-7e45-4811-b244-028ff3ed6e8c</t>
   </si>
   <si>
     <t>An energetic corporate sports video documenting Teleperformance Egypt's exciting football and padel tournament organized for company employees.
@@ -374,7 +364,7 @@
     <t>Teleperformance Egypt – Campus Career Fair</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1q7eW_7maawsOnyU2cyV3LKg_G6Iq8ltZ/view?usp=drive_link</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/4a0b4816-3052-453f-8833-37812b2ce080</t>
   </si>
   <si>
     <t>A dynamic promotional video capturing Teleperformance Egypt's recruitment presence and engagement across multiple university career fairs throughout Egypt.
@@ -388,7 +378,7 @@
     <t>Teleperformance Egypt – Alexandria Eid Al-Adha Celebration</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1V14on_KbudXbJy_MXB9BFRt14l0-EPxE/view?usp=sharing</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/df72f952-88e2-40b4-b07a-7375dc98fde8</t>
   </si>
   <si>
     <t>A festive corporate video capturing the high-energy Eid Al-Adha celebrations held for employees across Teleperformance branches in Alexandria.
@@ -402,7 +392,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
@@ -572,7 +562,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -867,7 +857,43 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Portfolio\Handover-20260625T210137Z-3-001\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{046A62C4-7C07-46EB-A98B-F1896C4878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79ED3A2B-08A0-4AB3-AA7B-289E1BF298E0}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C69FB52-47BE-4E5C-AE7B-A12FFEAE8C75}">
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/My portfolio.xlsx
+++ b/My portfolio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Masrya Short film </t>
   </si>
   <si>
-    <t>https://iframe.mediadelivery.net/embed/705832/72c22c06-4d6c-4c3f-940a-88c7e75f71f8</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/7c29b697-852d-4707-b815-991546159184</t>
   </si>
   <si>
     <t>A compelling anthology short film that highlights the vital role of women in Egyptian society by weaving together the distinct stories of multiple unique characters.
@@ -313,7 +313,7 @@
     <t>Teleperformance Egypt – Eid Al-Fitr Campaign</t>
   </si>
   <si>
-    <t>https://iframe.mediadelivery.net/embed/705832/492da76a-ebf1-4de0-a92a-81f2617892e5</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/3f795113-f5d9-4283-a223-dd9aa052c402</t>
   </si>
   <si>
     <t>A unique, fully AI-generated festive video created for Teleperformance Egypt to celebrate Eid Al-Fitr, designed to capture the holiday's joyful spirit through cutting-edge technology.
@@ -333,7 +333,7 @@
     <t>Teleperformance Egypt – Ramadan Charity Campaign</t>
   </si>
   <si>
-    <t>https://iframe.mediadelivery.net/embed/705832/19ad534b-93f0-433b-9fa8-dac091fc9181</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/909c2496-b7fd-42cb-9629-563ab5c55dee</t>
   </si>
   <si>
     <t>A heartwarming corporate social responsibility (CSR) video documenting Teleperformance Egypt's charity event, where employees gathered to pack Ramadan food boxes for families in need.
@@ -350,7 +350,7 @@
     <t>Teleperformance Egypt – Sports Tournament</t>
   </si>
   <si>
-    <t>https://iframe.mediadelivery.net/embed/705832/efc301ed-7e45-4811-b244-028ff3ed6e8c</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/abeb1252-2108-4871-ab50-c16e9565db07</t>
   </si>
   <si>
     <t>An energetic corporate sports video documenting Teleperformance Egypt's exciting football and padel tournament organized for company employees.
@@ -364,7 +364,7 @@
     <t>Teleperformance Egypt – Campus Career Fair</t>
   </si>
   <si>
-    <t>https://iframe.mediadelivery.net/embed/705832/4a0b4816-3052-453f-8833-37812b2ce080</t>
+    <t>https://iframe.mediadelivery.net/embed/705832/0665e2c5-5788-40fa-a7de-e0843b8ae2f4</t>
   </si>
   <si>
     <t>A dynamic promotional video capturing Teleperformance Egypt's recruitment presence and engagement across multiple university career fairs throughout Egypt.

--- a/My portfolio.xlsx
+++ b/My portfolio.xlsx
@@ -1,32 +1,42 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel Online</Application>
-  <Manager/>
-  <Company/>
-  <HyperlinkBase/>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Portfolio\Handover-20260625T210137Z-3-001\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A39FDF29-9D5E-4B12-A803-2D02C0A20AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79ED3A2B-08A0-4AB3-AA7B-289E1BF298E0}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:title/>
-  <dc:subject/>
-  <dc:creator>Islam Mohamed</dc:creator>
-  <cp:keywords/>
-  <dc:description/>
-  <cp:lastModifiedBy/>
-  <cp:revision/>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-06-25T23:08:56Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-29T09:27:26Z</dcterms:modified>
-  <cp:category/>
-  <cp:contentStatus/>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="108">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="112">
   <si>
     <t>Project Name</t>
   </si>
@@ -389,10 +399,23 @@
   <si>
     <t>https://www.facebook.com/100064726327101/videos/pcb.1429993362501528/1801425011215899</t>
   </si>
+  <si>
+    <t>Teleperformance Egypt – World Cup Coverage</t>
+  </si>
+  <si>
+    <t>https://player.mediadelivery.net/play/705832/c0654be0-6c83-40f4-a09d-8c39bb1c4f19</t>
+  </si>
+  <si>
+    <t>A fast-paced corporate highlight video capturing the high stakes, tension, and pure joy of Teleperformance Egypt employees during the World Cup.
+Highlights: Energetic cuts, stadium-like sound design, and vibrant color grading to showcase the electrifying workplace culture.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/r/1JyVnjHaXE/</t>
+  </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
@@ -446,7 +469,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -497,12 +520,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -543,6 +603,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -562,7 +644,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -857,43 +939,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30219"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Portfolio\Handover-20260625T210137Z-3-001\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{046A62C4-7C07-46EB-A98B-F1896C4878DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79ED3A2B-08A0-4AB3-AA7B-289E1BF298E0}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C69FB52-47BE-4E5C-AE7B-A12FFEAE8C75}">
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1649,43 +1695,58 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="183">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+    <row r="35" spans="1:7" ht="91.5">
+      <c r="A35" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4"/>
@@ -1750,8 +1811,10 @@
     <hyperlink ref="G33" r:id="rId45" xr:uid="{0D17FB24-10E5-48B8-BD09-38E9A642FBEA}"/>
     <hyperlink ref="B34" r:id="rId46" xr:uid="{E838C6F8-2138-4387-ACDC-A27BBFB44E3B}"/>
     <hyperlink ref="G30" r:id="rId47" xr:uid="{A4D831B2-0A55-49EB-834C-4393193A13D7}"/>
+    <hyperlink ref="G35" r:id="rId48" xr:uid="{1A9C0F64-5F05-48A5-A371-C4720CFA7587}"/>
+    <hyperlink ref="B35" r:id="rId49" xr:uid="{59C59C9A-24EF-4EFF-BDCD-BBB2613789F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId48"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId50"/>
 </worksheet>
 </file>